--- a/data/merged/2026-09-23/MERGED_FR_Mite-Vacuum_2026-09-23.xlsx
+++ b/data/merged/2026-09-23/MERGED_FR_Mite-Vacuum_2026-09-23.xlsx
@@ -3447,13 +3447,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>19</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
+      <xdr:rowOff>45000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>19</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
+      <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3491,13 +3491,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>20</xdr:row>
-      <xdr:rowOff>45000</xdr:rowOff>
+      <xdr:rowOff>44999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>20</xdr:row>
-      <xdr:rowOff>270000</xdr:rowOff>
+      <xdr:rowOff>269999</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3711,13 +3711,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>25</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
+      <xdr:rowOff>45000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>25</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
+      <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3975,13 +3975,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>31</xdr:row>
-      <xdr:rowOff>45000</xdr:rowOff>
+      <xdr:rowOff>44999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>31</xdr:row>
-      <xdr:rowOff>270000</xdr:rowOff>
+      <xdr:rowOff>269999</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4025,7 +4025,7 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>32</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
+      <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4113,7 +4113,7 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>34</xdr:row>
-      <xdr:rowOff>270000</xdr:rowOff>
+      <xdr:rowOff>269999</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4195,13 +4195,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>36</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
+      <xdr:rowOff>45000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>36</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
+      <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4262,50 +4262,6 @@
       </xdr:nvPicPr>
       <xdr:blipFill>
         <a:blip r:embed="rId37" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>38</xdr:row>
-      <xdr:rowOff>45000</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>38</xdr:row>
-      <xdr:rowOff>270000</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="38" name="Product 38">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <ns2:creationId id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId38" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -4647,7 +4603,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:BR39"/>
+  <dimension ref="A1:BR38"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="5" style="1" customWidth="1"/>
@@ -6230,7 +6186,7 @@
       <c r="B13" s="13"/>
       <c r="C13" s="14" t="inlineStr">
         <is>
-          <t>B0DWJQ9GFY</t>
+          <t>B0DX1WQJWN</t>
         </is>
       </c>
       <c r="D13" s="14"/>
@@ -6243,23 +6199,23 @@
       </c>
       <c r="H13" s="14" t="inlineStr">
         <is>
-          <t>Hocomay Aspirateur sans fil avec lumière UV-C, aspirateur à main 16 kPa avec écran LED, filtre HEPA, ultrasons, aspirateur de</t>
+          <t>Bear Aspirateur anti-acariens matelas, 15 kpa, 35000 tr/min, UV-C, punaises de lit, 99,9 % bactéries, allergènes, 4 m</t>
         </is>
       </c>
       <c r="I13" s="14"/>
       <c r="J13" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B0DWJQ9GFY?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0DX1WQJWN?psc=1</t>
         </is>
       </c>
       <c r="K13" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/61bbwwWUftL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/61nZHmsIS5L._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L13" s="14" t="inlineStr">
         <is>
-          <t>B0DWJQ9GFY</t>
+          <t>B0DX1WQJWN</t>
         </is>
       </c>
       <c r="M13" s="1"/>
@@ -6280,11 +6236,11 @@
       <c r="AB13"/>
       <c r="AC13"/>
       <c r="AD13" s="19">
-        <v>2</v>
+        <v>146</v>
       </c>
       <c r="AE13"/>
       <c r="AF13" s="20">
-        <v>3</v>
+        <v>4.6</v>
       </c>
       <c r="AG13" s="21">
         <v>0</v>
@@ -6336,7 +6292,7 @@
       <c r="B14" s="13"/>
       <c r="C14" s="14" t="inlineStr">
         <is>
-          <t>B0DX1WQJWN</t>
+          <t>B0F6MX5L26</t>
         </is>
       </c>
       <c r="D14" s="14"/>
@@ -6349,23 +6305,23 @@
       </c>
       <c r="H14" s="14" t="inlineStr">
         <is>
-          <t>Bear Aspirateur anti-acariens matelas, 15 kpa, 35000 tr/min, UV-C, punaises de lit, 99,9 % bactéries, allergènes, 4 m</t>
+          <t>JIGOO S100 Aspirateur de Matelas sans Fil：Aspirateur Anti-Acariens avec UV, 80000 TR/Min pour Nettoyage Profond des Matelas/L</t>
         </is>
       </c>
       <c r="I14" s="14"/>
       <c r="J14" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B0DX1WQJWN?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0F6MX5L26?psc=1</t>
         </is>
       </c>
       <c r="K14" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/61nZHmsIS5L._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71zSxKlDt9L._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L14" s="14" t="inlineStr">
         <is>
-          <t>B0DX1WQJWN</t>
+          <t>B0F6MX5L26</t>
         </is>
       </c>
       <c r="M14" s="1"/>
@@ -6386,11 +6342,11 @@
       <c r="AB14"/>
       <c r="AC14"/>
       <c r="AD14" s="19">
-        <v>146</v>
+        <v>99</v>
       </c>
       <c r="AE14"/>
       <c r="AF14" s="20">
-        <v>4.6</v>
+        <v>3.7</v>
       </c>
       <c r="AG14" s="21">
         <v>0</v>
@@ -6442,7 +6398,7 @@
       <c r="B15" s="13"/>
       <c r="C15" s="14" t="inlineStr">
         <is>
-          <t>B0F6MX5L26</t>
+          <t>B0F6XNKG8M</t>
         </is>
       </c>
       <c r="D15" s="14"/>
@@ -6455,23 +6411,23 @@
       </c>
       <c r="H15" s="14" t="inlineStr">
         <is>
-          <t>JIGOO S100 Aspirateur de Matelas sans Fil：Aspirateur Anti-Acariens avec UV, 80000 TR/Min pour Nettoyage Profond des Matelas/L</t>
+          <t>Tiazhan Aspirateur Matelas Anti Acariens, Lumière UV-C et 400 WsÉlimine 99,9% | Air Chaud à 60 °C, Filtre HEPA et Dépoussiér</t>
         </is>
       </c>
       <c r="I15" s="14"/>
       <c r="J15" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B0F6MX5L26?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0F6XNKG8M?psc=1</t>
         </is>
       </c>
       <c r="K15" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71zSxKlDt9L._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71iADJb-ECL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L15" s="14" t="inlineStr">
         <is>
-          <t>B0F6MX5L26</t>
+          <t>B0F6XNKG8M</t>
         </is>
       </c>
       <c r="M15" s="1"/>
@@ -6492,11 +6448,11 @@
       <c r="AB15"/>
       <c r="AC15"/>
       <c r="AD15" s="19">
-        <v>99</v>
+        <v>10</v>
       </c>
       <c r="AE15"/>
       <c r="AF15" s="20">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="AG15" s="21">
         <v>0</v>
@@ -6548,7 +6504,7 @@
       <c r="B16" s="13"/>
       <c r="C16" s="14" t="inlineStr">
         <is>
-          <t>B0F6XNKG8M</t>
+          <t>B0F9NJM4V9</t>
         </is>
       </c>
       <c r="D16" s="14"/>
@@ -6561,23 +6517,23 @@
       </c>
       <c r="H16" s="14" t="inlineStr">
         <is>
-          <t>Tiazhan Aspirateur Matelas Anti Acariens, Lumière UV-C et 400 WsÉlimine 99,9% | Air Chaud à 60 °C, Filtre HEPA et Dépoussiér</t>
+          <t>Liwankaqi Aspirateur anti-acariens pour matelas, avec UV C et ultrasons, aspiration 8 KPa, sans fil, anti-allergène, pour lit</t>
         </is>
       </c>
       <c r="I16" s="14"/>
       <c r="J16" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B0F6XNKG8M?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0F9NJM4V9?psc=1</t>
         </is>
       </c>
       <c r="K16" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71iADJb-ECL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/61GdOBS8v+L._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L16" s="14" t="inlineStr">
         <is>
-          <t>B0F6XNKG8M</t>
+          <t>B0F9NJM4V9</t>
         </is>
       </c>
       <c r="M16" s="1"/>
@@ -6598,11 +6554,11 @@
       <c r="AB16"/>
       <c r="AC16"/>
       <c r="AD16" s="19">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="AE16"/>
       <c r="AF16" s="20">
-        <v>3.8</v>
+        <v>2.5</v>
       </c>
       <c r="AG16" s="21">
         <v>0</v>
@@ -6654,7 +6610,7 @@
       <c r="B17" s="13"/>
       <c r="C17" s="14" t="inlineStr">
         <is>
-          <t>B0F9NJM4V9</t>
+          <t>B0FDWVV95V</t>
         </is>
       </c>
       <c r="D17" s="14"/>
@@ -6667,23 +6623,23 @@
       </c>
       <c r="H17" s="14" t="inlineStr">
         <is>
-          <t>Liwankaqi Aspirateur anti-acariens pour matelas, avec UV C et ultrasons, aspiration 8 KPa, sans fil, anti-allergène, pour lit</t>
+          <t>JIGOO T600 Aspirateur anti-acariens/Floral Delight (huile essentielle végétale)</t>
         </is>
       </c>
       <c r="I17" s="14"/>
       <c r="J17" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B0F9NJM4V9?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0FDWVV95V?psc=1</t>
         </is>
       </c>
       <c r="K17" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/61GdOBS8v+L._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/61tL+-AcL6L._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L17" s="14" t="inlineStr">
         <is>
-          <t>B0F9NJM4V9</t>
+          <t>B0FDWVV95V</t>
         </is>
       </c>
       <c r="M17" s="1"/>
@@ -6704,11 +6660,11 @@
       <c r="AB17"/>
       <c r="AC17"/>
       <c r="AD17" s="19">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="AE17"/>
       <c r="AF17" s="20">
-        <v>2.5</v>
+        <v>4.4</v>
       </c>
       <c r="AG17" s="21">
         <v>0</v>
@@ -6760,7 +6716,7 @@
       <c r="B18" s="13"/>
       <c r="C18" s="14" t="inlineStr">
         <is>
-          <t>B0FDWVV95V</t>
+          <t>B0FN3V6RFQ</t>
         </is>
       </c>
       <c r="D18" s="14"/>
@@ -6773,23 +6729,23 @@
       </c>
       <c r="H18" s="14" t="inlineStr">
         <is>
-          <t>JIGOO T600 Aspirateur anti-acariens/Floral Delight (huile essentielle végétale)</t>
+          <t>Minthouz Aspirateur Anti-acariens</t>
         </is>
       </c>
       <c r="I18" s="14"/>
       <c r="J18" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B0FDWVV95V?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0FN3V6RFQ?psc=1</t>
         </is>
       </c>
       <c r="K18" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/61tL+-AcL6L._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71YynWtKuIL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L18" s="14" t="inlineStr">
         <is>
-          <t>B0FDWVV95V</t>
+          <t>B0FN3V6RFQ</t>
         </is>
       </c>
       <c r="M18" s="1"/>
@@ -6810,11 +6766,11 @@
       <c r="AB18"/>
       <c r="AC18"/>
       <c r="AD18" s="19">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="AE18"/>
       <c r="AF18" s="20">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="AG18" s="21">
         <v>0</v>
@@ -6866,7 +6822,7 @@
       <c r="B19" s="13"/>
       <c r="C19" s="14" t="inlineStr">
         <is>
-          <t>B0FN3V6RFQ</t>
+          <t>B0FVS559GZ</t>
         </is>
       </c>
       <c r="D19" s="14"/>
@@ -6879,23 +6835,23 @@
       </c>
       <c r="H19" s="14" t="inlineStr">
         <is>
-          <t>Minthouz Aspirateur Anti-acariens</t>
+          <t>Yaasier Aspirateur Matelas, Aspirateur Anti-acariens pour Matelas avec lumière UV, Aspirateur à Main avec Filtre Hepa, Elimin</t>
         </is>
       </c>
       <c r="I19" s="14"/>
       <c r="J19" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B0FN3V6RFQ?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0FVS559GZ?psc=1</t>
         </is>
       </c>
       <c r="K19" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71YynWtKuIL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/51dJLeDXofL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L19" s="14" t="inlineStr">
         <is>
-          <t>B0FN3V6RFQ</t>
+          <t>B0FVS559GZ</t>
         </is>
       </c>
       <c r="M19" s="1"/>
@@ -6916,11 +6872,11 @@
       <c r="AB19"/>
       <c r="AC19"/>
       <c r="AD19" s="19">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AE19"/>
       <c r="AF19" s="20">
-        <v>4.3</v>
+        <v>3.6</v>
       </c>
       <c r="AG19" s="21">
         <v>0</v>
@@ -6972,7 +6928,7 @@
       <c r="B20" s="13"/>
       <c r="C20" s="14" t="inlineStr">
         <is>
-          <t>B0FVS559GZ</t>
+          <t>B0FY1MB1LJ</t>
         </is>
       </c>
       <c r="D20" s="14"/>
@@ -6985,23 +6941,23 @@
       </c>
       <c r="H20" s="14" t="inlineStr">
         <is>
-          <t>Yaasier Aspirateur Matelas, Aspirateur Anti-acariens pour Matelas avec lumière UV, Aspirateur à Main avec Filtre Hepa, Elimin</t>
+          <t>KOLERFLO Aspirateur Anti-acariens 3 en 1400WsUV-C + air Chaud 65°C, 16000Pa, 12000 Coups/Min, câble 5m, bac 350ml, élimine</t>
         </is>
       </c>
       <c r="I20" s="14"/>
       <c r="J20" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B0FVS559GZ?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0FY1MB1LJ?psc=1</t>
         </is>
       </c>
       <c r="K20" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/51dJLeDXofL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71JpIWC22rL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L20" s="14" t="inlineStr">
         <is>
-          <t>B0FVS559GZ</t>
+          <t>B0FY1MB1LJ</t>
         </is>
       </c>
       <c r="M20" s="1"/>
@@ -7026,7 +6982,7 @@
       </c>
       <c r="AE20"/>
       <c r="AF20" s="20">
-        <v>3.6</v>
+        <v>4.3</v>
       </c>
       <c r="AG20" s="21">
         <v>0</v>
@@ -7078,7 +7034,7 @@
       <c r="B21" s="13"/>
       <c r="C21" s="14" t="inlineStr">
         <is>
-          <t>B0FY1MB1LJ</t>
+          <t>B0FYM1D13D</t>
         </is>
       </c>
       <c r="D21" s="14"/>
@@ -7091,23 +7047,23 @@
       </c>
       <c r="H21" s="14" t="inlineStr">
         <is>
-          <t>KOLERFLO Aspirateur Anti-acariens 3 en 1400WsUV-C + air Chaud 65°C, 16000Pa, 12000 Coups/Min, câble 5m, bac 350ml, élimine</t>
+          <t>Aspirateur Matelas, Aspirateur Anti-acariens pour Matelas avec lumière UV, Aspirateur à Main avec Filtre Hepa, Elimine 99,99%</t>
         </is>
       </c>
       <c r="I21" s="14"/>
       <c r="J21" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B0FY1MB1LJ?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0FYM1D13D?psc=1</t>
         </is>
       </c>
       <c r="K21" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71JpIWC22rL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/51dJLeDXofL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L21" s="14" t="inlineStr">
         <is>
-          <t>B0FY1MB1LJ</t>
+          <t>B0FYM1D13D</t>
         </is>
       </c>
       <c r="M21" s="1"/>
@@ -7128,11 +7084,11 @@
       <c r="AB21"/>
       <c r="AC21"/>
       <c r="AD21" s="19">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="AE21"/>
       <c r="AF21" s="20">
-        <v>4.3</v>
+        <v>3</v>
       </c>
       <c r="AG21" s="21">
         <v>0</v>
@@ -7184,7 +7140,7 @@
       <c r="B22" s="13"/>
       <c r="C22" s="14" t="inlineStr">
         <is>
-          <t>B0FYM1D13D</t>
+          <t>B0G4RSJQVT</t>
         </is>
       </c>
       <c r="D22" s="14"/>
@@ -7197,23 +7153,23 @@
       </c>
       <c r="H22" s="14" t="inlineStr">
         <is>
-          <t>Aspirateur Matelas, Aspirateur Anti-acariens pour Matelas avec lumière UV, Aspirateur à Main avec Filtre Hepa, Elimine 99,99%</t>
+          <t>Lubluelu Aspirateur Anti-Acariens pour Matelas 3 en 1, 18 kPa Puissance d’Aspiration, Élimine 99% des Acariens et Allergènes,</t>
         </is>
       </c>
       <c r="I22" s="14"/>
       <c r="J22" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B0FYM1D13D?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0G4RSJQVT?psc=1</t>
         </is>
       </c>
       <c r="K22" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/51dJLeDXofL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71mJa10XC6L._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L22" s="14" t="inlineStr">
         <is>
-          <t>B0FYM1D13D</t>
+          <t>B0G4RSJQVT</t>
         </is>
       </c>
       <c r="M22" s="1"/>
@@ -7234,11 +7190,11 @@
       <c r="AB22"/>
       <c r="AC22"/>
       <c r="AD22" s="19">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="AE22"/>
       <c r="AF22" s="20">
-        <v>3</v>
+        <v>4.6</v>
       </c>
       <c r="AG22" s="21">
         <v>0</v>
@@ -7290,7 +7246,7 @@
       <c r="B23" s="13"/>
       <c r="C23" s="14" t="inlineStr">
         <is>
-          <t>B0G4RSJQVT</t>
+          <t>B0GF7CNTYL</t>
         </is>
       </c>
       <c r="D23" s="14"/>
@@ -7303,23 +7259,23 @@
       </c>
       <c r="H23" s="14" t="inlineStr">
         <is>
-          <t>Lubluelu Aspirateur Anti-Acariens pour Matelas 3 en 1, 18 kPa Puissance d’Aspiration, Élimine 99% des Acariens et Allergènes,</t>
+          <t>Aspirateur de Matelas UV-C Ultrasonique pour Lit et CanapésAspirateur sans fil pour housses de couette, matelas, canapés en</t>
         </is>
       </c>
       <c r="I23" s="14"/>
       <c r="J23" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B0G4RSJQVT?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0GF7CNTYL?psc=1</t>
         </is>
       </c>
       <c r="K23" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71mJa10XC6L._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71H9bRmoUnL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L23" s="14" t="inlineStr">
         <is>
-          <t>B0G4RSJQVT</t>
+          <t>B0GF7CNTYL</t>
         </is>
       </c>
       <c r="M23" s="1"/>
@@ -7339,13 +7295,9 @@
       <c r="AA23"/>
       <c r="AB23"/>
       <c r="AC23"/>
-      <c r="AD23" s="19">
-        <v>26</v>
-      </c>
+      <c r="AD23" s="19"/>
       <c r="AE23"/>
-      <c r="AF23" s="20">
-        <v>4.6</v>
-      </c>
+      <c r="AF23" s="20"/>
       <c r="AG23" s="21">
         <v>0</v>
       </c>
@@ -7396,7 +7348,7 @@
       <c r="B24" s="13"/>
       <c r="C24" s="14" t="inlineStr">
         <is>
-          <t>B0GF7CNTYL</t>
+          <t>B0GGBLWNRZ</t>
         </is>
       </c>
       <c r="D24" s="14"/>
@@ -7409,23 +7361,23 @@
       </c>
       <c r="H24" s="14" t="inlineStr">
         <is>
-          <t>Aspirateur de Matelas UV-C Ultrasonique pour Lit et CanapésAspirateur sans fil pour housses de couette, matelas, canapés en</t>
+          <t>Ubric Aspirateur sans fil anti-acariens, avec filtre HEPA, aspirateur de matelas sans fil pour matelas, canapé, coussin, tapi</t>
         </is>
       </c>
       <c r="I24" s="14"/>
       <c r="J24" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B0GF7CNTYL?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0GGBLWNRZ?psc=1</t>
         </is>
       </c>
       <c r="K24" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71H9bRmoUnL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/41xNIs1B-1L._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L24" s="14" t="inlineStr">
         <is>
-          <t>B0GF7CNTYL</t>
+          <t>B0GGBLWNRZ</t>
         </is>
       </c>
       <c r="M24" s="1"/>
@@ -7445,9 +7397,13 @@
       <c r="AA24"/>
       <c r="AB24"/>
       <c r="AC24"/>
-      <c r="AD24" s="19"/>
+      <c r="AD24" s="19">
+        <v>2</v>
+      </c>
       <c r="AE24"/>
-      <c r="AF24" s="20"/>
+      <c r="AF24" s="20">
+        <v>3</v>
+      </c>
       <c r="AG24" s="21">
         <v>0</v>
       </c>
@@ -7498,7 +7454,7 @@
       <c r="B25" s="13"/>
       <c r="C25" s="14" t="inlineStr">
         <is>
-          <t>B0GGBLWNRZ</t>
+          <t>B0GMPVWCZM</t>
         </is>
       </c>
       <c r="D25" s="14"/>
@@ -7511,23 +7467,23 @@
       </c>
       <c r="H25" s="14" t="inlineStr">
         <is>
-          <t>Ubric Aspirateur sans fil anti-acariens, avec filtre HEPA, aspirateur de matelas sans fil pour matelas, canapé, coussin, tapi</t>
+          <t>Elecbee Aspirateur anti-acariens sans fil pour matelas, aspirateur anti-acariens avec lumière UV, indicateur LED, technologie</t>
         </is>
       </c>
       <c r="I25" s="14"/>
       <c r="J25" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B0GGBLWNRZ?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0GMPVWCZM?psc=1</t>
         </is>
       </c>
       <c r="K25" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/41xNIs1B-1L._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/81J2yw2XZnL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L25" s="14" t="inlineStr">
         <is>
-          <t>B0GGBLWNRZ</t>
+          <t>B0GMPVWCZM</t>
         </is>
       </c>
       <c r="M25" s="1"/>
@@ -7552,7 +7508,7 @@
       </c>
       <c r="AE25"/>
       <c r="AF25" s="20">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AG25" s="21">
         <v>0</v>
@@ -7604,7 +7560,7 @@
       <c r="B26" s="13"/>
       <c r="C26" s="14" t="inlineStr">
         <is>
-          <t>B0GMPVWCZM</t>
+          <t>B0GQSRHH7M</t>
         </is>
       </c>
       <c r="D26" s="14"/>
@@ -7617,23 +7573,23 @@
       </c>
       <c r="H26" s="14" t="inlineStr">
         <is>
-          <t>Elecbee Aspirateur anti-acariens sans fil pour matelas, aspirateur anti-acariens avec lumière UV, indicateur LED, technologie</t>
+          <t>Resmafn 15KPa Aspirateur Anti Acariens avec UV-C et 5M FilsAspirateur Lit, 60°C Chaleur, Réservoir Amovible 1L avec Filtre,</t>
         </is>
       </c>
       <c r="I26" s="14"/>
       <c r="J26" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B0GMPVWCZM?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0GQSRHH7M?psc=1</t>
         </is>
       </c>
       <c r="K26" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/81J2yw2XZnL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/61BzcWHyvIL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L26" s="14" t="inlineStr">
         <is>
-          <t>B0GMPVWCZM</t>
+          <t>B0GQSRHH7M</t>
         </is>
       </c>
       <c r="M26" s="1"/>
@@ -7654,11 +7610,11 @@
       <c r="AB26"/>
       <c r="AC26"/>
       <c r="AD26" s="19">
-        <v>2</v>
+        <v>149</v>
       </c>
       <c r="AE26"/>
       <c r="AF26" s="20">
-        <v>5</v>
+        <v>4.1</v>
       </c>
       <c r="AG26" s="21">
         <v>0</v>
@@ -7710,7 +7666,7 @@
       <c r="B27" s="13"/>
       <c r="C27" s="14" t="inlineStr">
         <is>
-          <t>B0GQSRHH7M</t>
+          <t>B0GT17NK5X</t>
         </is>
       </c>
       <c r="D27" s="14"/>
@@ -7723,23 +7679,23 @@
       </c>
       <c r="H27" s="14" t="inlineStr">
         <is>
-          <t>Resmafn 15KPa Aspirateur Anti Acariens avec UV-C et 5M FilsAspirateur Lit, 60°C Chaleur, Réservoir Amovible 1L avec Filtre,</t>
+          <t>Aspirateur anti-acariens sans fil pour matelas, avec lumière UV de 253,7 nm, ultrasons et tapotements de rouleau de brosse, a</t>
         </is>
       </c>
       <c r="I27" s="14"/>
       <c r="J27" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B0GQSRHH7M?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0GT17NK5X?psc=1</t>
         </is>
       </c>
       <c r="K27" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/61BzcWHyvIL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71ZkgBFQnaL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L27" s="14" t="inlineStr">
         <is>
-          <t>B0GQSRHH7M</t>
+          <t>B0GT17NK5X</t>
         </is>
       </c>
       <c r="M27" s="1"/>
@@ -7760,11 +7716,11 @@
       <c r="AB27"/>
       <c r="AC27"/>
       <c r="AD27" s="19">
-        <v>149</v>
+        <v>1</v>
       </c>
       <c r="AE27"/>
       <c r="AF27" s="20">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="AG27" s="21">
         <v>0</v>
@@ -7816,7 +7772,7 @@
       <c r="B28" s="13"/>
       <c r="C28" s="14" t="inlineStr">
         <is>
-          <t>B0GT17NK5X</t>
+          <t>B0GTYZLWW3</t>
         </is>
       </c>
       <c r="D28" s="14"/>
@@ -7829,23 +7785,23 @@
       </c>
       <c r="H28" s="14" t="inlineStr">
         <is>
-          <t>Aspirateur anti-acariens sans fil pour matelas, avec lumière UV de 253,7 nm, ultrasons et tapotements de rouleau de brosse, a</t>
+          <t>Vehiwell Aspirateur anti-acariens, nettoyeur de matelas 15 kPa avec lumière UV-C</t>
         </is>
       </c>
       <c r="I28" s="14"/>
       <c r="J28" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B0GT17NK5X?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0GTYZLWW3?psc=1</t>
         </is>
       </c>
       <c r="K28" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71ZkgBFQnaL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71RQJ5XzBgL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L28" s="14" t="inlineStr">
         <is>
-          <t>B0GT17NK5X</t>
+          <t>B0GTYZLWW3</t>
         </is>
       </c>
       <c r="M28" s="1"/>
@@ -7865,13 +7821,9 @@
       <c r="AA28"/>
       <c r="AB28"/>
       <c r="AC28"/>
-      <c r="AD28" s="19">
-        <v>1</v>
-      </c>
+      <c r="AD28" s="19"/>
       <c r="AE28"/>
-      <c r="AF28" s="20">
-        <v>5</v>
-      </c>
+      <c r="AF28" s="20"/>
       <c r="AG28" s="21">
         <v>0</v>
       </c>
@@ -7922,7 +7874,7 @@
       <c r="B29" s="13"/>
       <c r="C29" s="14" t="inlineStr">
         <is>
-          <t>B0GTYZLWW3</t>
+          <t>B0GWD94VPC</t>
         </is>
       </c>
       <c r="D29" s="14"/>
@@ -7935,23 +7887,23 @@
       </c>
       <c r="H29" s="14" t="inlineStr">
         <is>
-          <t>Vehiwell Aspirateur anti-acariens, nettoyeur de matelas 15 kPa avec lumière UV-C</t>
+          <t>JIGOO Aspirateur Anti-acariens T600 pour Matelas, 700 W, avec lumière UV, 15 kPa, Aspiration des acariens, élimine 99,9%, Aff</t>
         </is>
       </c>
       <c r="I29" s="14"/>
       <c r="J29" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B0GTYZLWW3?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0GWD94VPC?psc=1</t>
         </is>
       </c>
       <c r="K29" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71RQJ5XzBgL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/713CpLpTocL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L29" s="14" t="inlineStr">
         <is>
-          <t>B0GTYZLWW3</t>
+          <t>B0GWD94VPC</t>
         </is>
       </c>
       <c r="M29" s="1"/>
@@ -7967,7 +7919,9 @@
       <c r="W29" s="15"/>
       <c r="X29" s="15"/>
       <c r="Y29"/>
-      <c r="Z29" s="4"/>
+      <c r="Z29" s="4">
+        <v>127.44</v>
+      </c>
       <c r="AA29"/>
       <c r="AB29"/>
       <c r="AC29"/>
@@ -8024,7 +7978,7 @@
       <c r="B30" s="13"/>
       <c r="C30" s="14" t="inlineStr">
         <is>
-          <t>B0GWD94VPC</t>
+          <t>B0GWH1FGJB</t>
         </is>
       </c>
       <c r="D30" s="14"/>
@@ -8037,23 +7991,23 @@
       </c>
       <c r="H30" s="14" t="inlineStr">
         <is>
-          <t>JIGOO Aspirateur Anti-acariens T600 pour Matelas, 700 W, avec lumière UV, 15 kPa, Aspiration des acariens, élimine 99,9%, Aff</t>
+          <t>Aspirateur anti-acariens 2 en 1 pour matelas, stérilisation à lumière bleue et haute fréquence, puissant nettoyeur de matelas</t>
         </is>
       </c>
       <c r="I30" s="14"/>
       <c r="J30" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B0GWD94VPC?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0GWH1FGJB?psc=1</t>
         </is>
       </c>
       <c r="K30" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/713CpLpTocL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/61J8ToT-vJL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L30" s="14" t="inlineStr">
         <is>
-          <t>B0GWD94VPC</t>
+          <t>B0GWH1FGJB</t>
         </is>
       </c>
       <c r="M30" s="1"/>
@@ -8069,9 +8023,7 @@
       <c r="W30" s="15"/>
       <c r="X30" s="15"/>
       <c r="Y30"/>
-      <c r="Z30" s="4">
-        <v>127.44</v>
-      </c>
+      <c r="Z30" s="4"/>
       <c r="AA30"/>
       <c r="AB30"/>
       <c r="AC30"/>
@@ -8128,7 +8080,7 @@
       <c r="B31" s="13"/>
       <c r="C31" s="14" t="inlineStr">
         <is>
-          <t>B0GWH1FGJB</t>
+          <t>B0GX27JHM5</t>
         </is>
       </c>
       <c r="D31" s="14"/>
@@ -8141,23 +8093,23 @@
       </c>
       <c r="H31" s="14" t="inlineStr">
         <is>
-          <t>Aspirateur anti-acariens 2 en 1 pour matelas, stérilisation à lumière bleue et haute fréquence, puissant nettoyeur de matelas</t>
+          <t>CREATULIZE X1 Aspirateur Matelas Robot sans FilsNavigation Intelligente, Évitement d'obstacles, Lumière UV-C 270 Nm, 14AW,</t>
         </is>
       </c>
       <c r="I31" s="14"/>
       <c r="J31" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B0GWH1FGJB?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0GX27JHM5?psc=1</t>
         </is>
       </c>
       <c r="K31" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/61J8ToT-vJL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/61ZZVDtLmcL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L31" s="14" t="inlineStr">
         <is>
-          <t>B0GWH1FGJB</t>
+          <t>B0GX27JHM5</t>
         </is>
       </c>
       <c r="M31" s="1"/>
@@ -8177,9 +8129,13 @@
       <c r="AA31"/>
       <c r="AB31"/>
       <c r="AC31"/>
-      <c r="AD31" s="19"/>
+      <c r="AD31" s="19">
+        <v>27</v>
+      </c>
       <c r="AE31"/>
-      <c r="AF31" s="20"/>
+      <c r="AF31" s="20">
+        <v>4.3</v>
+      </c>
       <c r="AG31" s="21">
         <v>0</v>
       </c>
@@ -8230,7 +8186,7 @@
       <c r="B32" s="13"/>
       <c r="C32" s="14" t="inlineStr">
         <is>
-          <t>B0GX27JHM5</t>
+          <t>B0GYS43G8G</t>
         </is>
       </c>
       <c r="D32" s="14"/>
@@ -8243,23 +8199,23 @@
       </c>
       <c r="H32" s="14" t="inlineStr">
         <is>
-          <t>CREATULIZE X1 Aspirateur Matelas Robot sans FilsNavigation Intelligente, Évitement d'obstacles, Lumière UV-C 270 Nm, 14AW,</t>
+          <t>Aspirateur Matelas, Aspirateur Anti-Acariens, Vibration Haute Fréquence, Filtrage Trois Niveaux, Filtre Lavable, pour Canapés</t>
         </is>
       </c>
       <c r="I32" s="14"/>
       <c r="J32" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B0GX27JHM5?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0GYS43G8G?psc=1</t>
         </is>
       </c>
       <c r="K32" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/61ZZVDtLmcL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/51JXrvAAoZL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L32" s="14" t="inlineStr">
         <is>
-          <t>B0GX27JHM5</t>
+          <t>B0GYS43G8G</t>
         </is>
       </c>
       <c r="M32" s="1"/>
@@ -8280,11 +8236,11 @@
       <c r="AB32"/>
       <c r="AC32"/>
       <c r="AD32" s="19">
-        <v>27</v>
+        <v>2</v>
       </c>
       <c r="AE32"/>
       <c r="AF32" s="20">
-        <v>4.3</v>
+        <v>1</v>
       </c>
       <c r="AG32" s="21">
         <v>0</v>
@@ -8336,7 +8292,7 @@
       <c r="B33" s="13"/>
       <c r="C33" s="14" t="inlineStr">
         <is>
-          <t>B0GYS43G8G</t>
+          <t>B0H1HSF3G6</t>
         </is>
       </c>
       <c r="D33" s="14"/>
@@ -8349,23 +8305,23 @@
       </c>
       <c r="H33" s="14" t="inlineStr">
         <is>
-          <t>Aspirateur Matelas, Aspirateur Anti-Acariens, Vibration Haute Fréquence, Filtrage Trois Niveaux, Filtre Lavable, pour Canapés</t>
+          <t>Circlio V20 Pro 18kPa Aspirateur Anti Acariens pour Matelas avec Lumière UVsDouble bac à Poussière | Punaise de Lit élimine</t>
         </is>
       </c>
       <c r="I33" s="14"/>
       <c r="J33" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B0GYS43G8G?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0H1HSF3G6?psc=1</t>
         </is>
       </c>
       <c r="K33" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/51JXrvAAoZL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71bkUyyVyuL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L33" s="14" t="inlineStr">
         <is>
-          <t>B0GYS43G8G</t>
+          <t>B0H1HSF3G6</t>
         </is>
       </c>
       <c r="M33" s="1"/>
@@ -8386,11 +8342,11 @@
       <c r="AB33"/>
       <c r="AC33"/>
       <c r="AD33" s="19">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="AE33"/>
       <c r="AF33" s="20">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AG33" s="21">
         <v>0</v>
@@ -8442,7 +8398,7 @@
       <c r="B34" s="13"/>
       <c r="C34" s="14" t="inlineStr">
         <is>
-          <t>B0H1HSF3G6</t>
+          <t>B0H418FY5Y</t>
         </is>
       </c>
       <c r="D34" s="14"/>
@@ -8455,23 +8411,23 @@
       </c>
       <c r="H34" s="14" t="inlineStr">
         <is>
-          <t>Circlio V20 Pro 18kPa Aspirateur Anti Acariens pour Matelas avec Lumière UVsDouble bac à Poussière | Punaise de Lit élimine</t>
+          <t>Lubluelu Aspirateur Anti-Acariens 20 kPa, 600 W, 65 000 Coups/Min, UV-CsAspirateur matelas nettoyage en profondeur, double</t>
         </is>
       </c>
       <c r="I34" s="14"/>
       <c r="J34" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B0H1HSF3G6?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0H418FY5Y?psc=1</t>
         </is>
       </c>
       <c r="K34" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71bkUyyVyuL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/61InrYvl2-L._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L34" s="14" t="inlineStr">
         <is>
-          <t>B0H1HSF3G6</t>
+          <t>B0H418FY5Y</t>
         </is>
       </c>
       <c r="M34" s="1"/>
@@ -8492,11 +8448,11 @@
       <c r="AB34"/>
       <c r="AC34"/>
       <c r="AD34" s="19">
-        <v>10</v>
+        <v>69</v>
       </c>
       <c r="AE34"/>
       <c r="AF34" s="20">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="AG34" s="21">
         <v>0</v>
@@ -8548,7 +8504,7 @@
       <c r="B35" s="13"/>
       <c r="C35" s="14" t="inlineStr">
         <is>
-          <t>B0H418FY5Y</t>
+          <t>B0H6F2NPXK</t>
         </is>
       </c>
       <c r="D35" s="14"/>
@@ -8561,13 +8517,13 @@
       </c>
       <c r="H35" s="14" t="inlineStr">
         <is>
-          <t>Lubluelu Aspirateur Anti-Acariens 20 kPa, 600 W, 65 000 Coups/Min, UV-CsAspirateur matelas nettoyage en profondeur, double</t>
+          <t>Lubluelu Nettoyeur de matelas 3 en 1 20 kPa, aspirateur anti-acariens avec fonction de frappe et fonction chauffante, aspirat</t>
         </is>
       </c>
       <c r="I35" s="14"/>
       <c r="J35" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B0H418FY5Y?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0H6F2NPXK?psc=1</t>
         </is>
       </c>
       <c r="K35" s="14" t="inlineStr">
@@ -8577,7 +8533,7 @@
       </c>
       <c r="L35" s="14" t="inlineStr">
         <is>
-          <t>B0H418FY5Y</t>
+          <t>B0H6F2NPXK</t>
         </is>
       </c>
       <c r="M35" s="1"/>
@@ -8598,7 +8554,7 @@
       <c r="AB35"/>
       <c r="AC35"/>
       <c r="AD35" s="19">
-        <v>69</v>
+        <v>15</v>
       </c>
       <c r="AE35"/>
       <c r="AF35" s="20">
@@ -8654,7 +8610,7 @@
       <c r="B36" s="13"/>
       <c r="C36" s="14" t="inlineStr">
         <is>
-          <t>B0H6F2NPXK</t>
+          <t>B0H7WRJXL5</t>
         </is>
       </c>
       <c r="D36" s="14"/>
@@ -8667,23 +8623,23 @@
       </c>
       <c r="H36" s="14" t="inlineStr">
         <is>
-          <t>Lubluelu Nettoyeur de matelas 3 en 1 20 kPa, aspirateur anti-acariens avec fonction de frappe et fonction chauffante, aspirat</t>
+          <t>Beghdhu Aspirateur pour Matelas avec lumière UVsAspirateur à main pour matelas, lit, canapé 20 kPa</t>
         </is>
       </c>
       <c r="I36" s="14"/>
       <c r="J36" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B0H6F2NPXK?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0H7WRJXL5?psc=1</t>
         </is>
       </c>
       <c r="K36" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/61InrYvl2-L._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71pvlE5JbtL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L36" s="14" t="inlineStr">
         <is>
-          <t>B0H6F2NPXK</t>
+          <t>B0H7WRJXL5</t>
         </is>
       </c>
       <c r="M36" s="1"/>
@@ -8704,11 +8660,11 @@
       <c r="AB36"/>
       <c r="AC36"/>
       <c r="AD36" s="19">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="AE36"/>
       <c r="AF36" s="20">
-        <v>4.6</v>
+        <v>2</v>
       </c>
       <c r="AG36" s="21">
         <v>0</v>
@@ -8760,7 +8716,7 @@
       <c r="B37" s="13"/>
       <c r="C37" s="14" t="inlineStr">
         <is>
-          <t>B0H7WRJXL5</t>
+          <t>B0H8Z6R4ZK</t>
         </is>
       </c>
       <c r="D37" s="14"/>
@@ -8773,23 +8729,23 @@
       </c>
       <c r="H37" s="14" t="inlineStr">
         <is>
-          <t>Beghdhu Aspirateur pour Matelas avec lumière UVsAspirateur à main pour matelas, lit, canapé 20 kPa</t>
+          <t>Aspirateur de matelas portable sans fil rechargeable pour lits, canapéssAspirateur à main silencieux, nettoyeur en profonde</t>
         </is>
       </c>
       <c r="I37" s="14"/>
       <c r="J37" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B0H7WRJXL5?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0H8Z6R4ZK?psc=1</t>
         </is>
       </c>
       <c r="K37" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71pvlE5JbtL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/61HKr6BnAHL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L37" s="14" t="inlineStr">
         <is>
-          <t>B0H7WRJXL5</t>
+          <t>B0H8Z6R4ZK</t>
         </is>
       </c>
       <c r="M37" s="1"/>
@@ -8809,13 +8765,9 @@
       <c r="AA37"/>
       <c r="AB37"/>
       <c r="AC37"/>
-      <c r="AD37" s="19">
-        <v>2</v>
-      </c>
+      <c r="AD37" s="19"/>
       <c r="AE37"/>
-      <c r="AF37" s="20">
-        <v>2</v>
-      </c>
+      <c r="AF37" s="20"/>
       <c r="AG37" s="21">
         <v>0</v>
       </c>
@@ -8866,7 +8818,7 @@
       <c r="B38" s="13"/>
       <c r="C38" s="14" t="inlineStr">
         <is>
-          <t>B0H8Z6R4ZK</t>
+          <t>B0HG11J16S</t>
         </is>
       </c>
       <c r="D38" s="14"/>
@@ -8879,23 +8831,23 @@
       </c>
       <c r="H38" s="14" t="inlineStr">
         <is>
-          <t>Aspirateur de matelas portable sans fil rechargeable pour lits, canapéssAspirateur à main silencieux, nettoyeur en profonde</t>
+          <t>Beghdhu Aspirateur pour Matelas avec lumière UVsAspirateur à main pour matelas, lit, canapé 20 kPa</t>
         </is>
       </c>
       <c r="I38" s="14"/>
       <c r="J38" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B0H8Z6R4ZK?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0HG11J16S?psc=1</t>
         </is>
       </c>
       <c r="K38" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/61HKr6BnAHL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71pvlE5JbtL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L38" s="14" t="inlineStr">
         <is>
-          <t>B0H8Z6R4ZK</t>
+          <t>B0HG11J16S</t>
         </is>
       </c>
       <c r="M38" s="1"/>
@@ -8915,9 +8867,13 @@
       <c r="AA38"/>
       <c r="AB38"/>
       <c r="AC38"/>
-      <c r="AD38" s="19"/>
+      <c r="AD38" s="19">
+        <v>2</v>
+      </c>
       <c r="AE38"/>
-      <c r="AF38" s="20"/>
+      <c r="AF38" s="20">
+        <v>1</v>
+      </c>
       <c r="AG38" s="21">
         <v>0</v>
       </c>
@@ -8960,112 +8916,6 @@
       <c r="BP38"/>
       <c r="BQ38" s="22"/>
       <c r="BR38"/>
-    </row>
-    <row r="39" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="13">
-        <v>38</v>
-      </c>
-      <c r="B39" s="13"/>
-      <c r="C39" s="14" t="inlineStr">
-        <is>
-          <t>B0HG11J16S</t>
-        </is>
-      </c>
-      <c r="D39" s="14"/>
-      <c r="E39" s="14"/>
-      <c r="F39"/>
-      <c r="G39" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.frundefined</t>
-        </is>
-      </c>
-      <c r="H39" s="14" t="inlineStr">
-        <is>
-          <t>Beghdhu Aspirateur pour Matelas avec lumière UVsAspirateur à main pour matelas, lit, canapé 20 kPa</t>
-        </is>
-      </c>
-      <c r="I39" s="14"/>
-      <c r="J39" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.fr/dp/B0HG11J16S?psc=1</t>
-        </is>
-      </c>
-      <c r="K39" s="14" t="inlineStr">
-        <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71pvlE5JbtL._AC_UL300_SR300,200_.jpg</t>
-        </is>
-      </c>
-      <c r="L39" s="14" t="inlineStr">
-        <is>
-          <t>B0HG11J16S</t>
-        </is>
-      </c>
-      <c r="M39" s="1"/>
-      <c r="N39" s="14"/>
-      <c r="O39" s="15"/>
-      <c r="P39" s="15"/>
-      <c r="Q39" s="16"/>
-      <c r="R39" s="17"/>
-      <c r="S39" s="18"/>
-      <c r="T39" s="15"/>
-      <c r="U39" s="16"/>
-      <c r="V39" s="15"/>
-      <c r="W39" s="15"/>
-      <c r="X39" s="15"/>
-      <c r="Y39"/>
-      <c r="Z39" s="4"/>
-      <c r="AA39"/>
-      <c r="AB39"/>
-      <c r="AC39"/>
-      <c r="AD39" s="19">
-        <v>2</v>
-      </c>
-      <c r="AE39"/>
-      <c r="AF39" s="20">
-        <v>1</v>
-      </c>
-      <c r="AG39" s="21">
-        <v>0</v>
-      </c>
-      <c r="AH39"/>
-      <c r="AI39" s="16">
-        <v>0</v>
-      </c>
-      <c r="AJ39"/>
-      <c r="AK39" s="1"/>
-      <c r="AL39" s="19"/>
-      <c r="AM39"/>
-      <c r="AN39" s="13"/>
-      <c r="AO39" s="13"/>
-      <c r="AP39"/>
-      <c r="AQ39" s="19"/>
-      <c r="AR39"/>
-      <c r="AS39"/>
-      <c r="AT39"/>
-      <c r="AU39" s="13"/>
-      <c r="AV39" s="14"/>
-      <c r="AW39" s="13"/>
-      <c r="AX39" s="13"/>
-      <c r="AY39" s="13"/>
-      <c r="AZ39" s="13"/>
-      <c r="BA39" s="13"/>
-      <c r="BB39" s="13"/>
-      <c r="BC39" s="13"/>
-      <c r="BD39" s="13"/>
-      <c r="BE39" s="13"/>
-      <c r="BF39" s="13"/>
-      <c r="BG39" s="13"/>
-      <c r="BH39" s="14"/>
-      <c r="BI39"/>
-      <c r="BJ39"/>
-      <c r="BK39" s="22"/>
-      <c r="BL39"/>
-      <c r="BM39" s="22"/>
-      <c r="BN39"/>
-      <c r="BO39" s="22"/>
-      <c r="BP39"/>
-      <c r="BQ39" s="22"/>
-      <c r="BR39"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -9126,143 +8976,138 @@
     <hyperlink ref="J12" r:id="rId53" tooltip="https://www.amazon.fr/dp/B0DTPDTR73?psc=1"/>
     <hyperlink ref="K12" r:id="rId54" tooltip="https://images-eu.ssl-images-amazon.com/images/I/616ONjp63mL._AC_UL300_SR300,200_.jpg"/>
     <hyperlink ref="L12" r:id="rId55" tooltip="https://www.amazon.fr/dp/B0DTPDTR73"/>
-    <hyperlink ref="C13" r:id="rId56" tooltip="https://www.amazon.fr/dp/B0DWJQ9GFY"/>
+    <hyperlink ref="C13" r:id="rId56" tooltip="https://www.amazon.fr/dp/B0DX1WQJWN"/>
     <hyperlink ref="G13" r:id="rId57" tooltip="https://www.amazon.frundefined"/>
-    <hyperlink ref="J13" r:id="rId58" tooltip="https://www.amazon.fr/dp/B0DWJQ9GFY?psc=1"/>
-    <hyperlink ref="K13" r:id="rId59" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61bbwwWUftL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L13" r:id="rId60" tooltip="https://www.amazon.fr/dp/B0DWJQ9GFY"/>
-    <hyperlink ref="C14" r:id="rId61" tooltip="https://www.amazon.fr/dp/B0DX1WQJWN"/>
+    <hyperlink ref="J13" r:id="rId58" tooltip="https://www.amazon.fr/dp/B0DX1WQJWN?psc=1"/>
+    <hyperlink ref="K13" r:id="rId59" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61nZHmsIS5L._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L13" r:id="rId60" tooltip="https://www.amazon.fr/dp/B0DX1WQJWN"/>
+    <hyperlink ref="C14" r:id="rId61" tooltip="https://www.amazon.fr/dp/B0F6MX5L26"/>
     <hyperlink ref="G14" r:id="rId62" tooltip="https://www.amazon.frundefined"/>
-    <hyperlink ref="J14" r:id="rId63" tooltip="https://www.amazon.fr/dp/B0DX1WQJWN?psc=1"/>
-    <hyperlink ref="K14" r:id="rId64" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61nZHmsIS5L._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L14" r:id="rId65" tooltip="https://www.amazon.fr/dp/B0DX1WQJWN"/>
-    <hyperlink ref="C15" r:id="rId66" tooltip="https://www.amazon.fr/dp/B0F6MX5L26"/>
+    <hyperlink ref="J14" r:id="rId63" tooltip="https://www.amazon.fr/dp/B0F6MX5L26?psc=1"/>
+    <hyperlink ref="K14" r:id="rId64" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71zSxKlDt9L._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L14" r:id="rId65" tooltip="https://www.amazon.fr/dp/B0F6MX5L26"/>
+    <hyperlink ref="C15" r:id="rId66" tooltip="https://www.amazon.fr/dp/B0F6XNKG8M"/>
     <hyperlink ref="G15" r:id="rId67" tooltip="https://www.amazon.frundefined"/>
-    <hyperlink ref="J15" r:id="rId68" tooltip="https://www.amazon.fr/dp/B0F6MX5L26?psc=1"/>
-    <hyperlink ref="K15" r:id="rId69" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71zSxKlDt9L._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L15" r:id="rId70" tooltip="https://www.amazon.fr/dp/B0F6MX5L26"/>
-    <hyperlink ref="C16" r:id="rId71" tooltip="https://www.amazon.fr/dp/B0F6XNKG8M"/>
+    <hyperlink ref="J15" r:id="rId68" tooltip="https://www.amazon.fr/dp/B0F6XNKG8M?psc=1"/>
+    <hyperlink ref="K15" r:id="rId69" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71iADJb-ECL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L15" r:id="rId70" tooltip="https://www.amazon.fr/dp/B0F6XNKG8M"/>
+    <hyperlink ref="C16" r:id="rId71" tooltip="https://www.amazon.fr/dp/B0F9NJM4V9"/>
     <hyperlink ref="G16" r:id="rId72" tooltip="https://www.amazon.frundefined"/>
-    <hyperlink ref="J16" r:id="rId73" tooltip="https://www.amazon.fr/dp/B0F6XNKG8M?psc=1"/>
-    <hyperlink ref="K16" r:id="rId74" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71iADJb-ECL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L16" r:id="rId75" tooltip="https://www.amazon.fr/dp/B0F6XNKG8M"/>
-    <hyperlink ref="C17" r:id="rId76" tooltip="https://www.amazon.fr/dp/B0F9NJM4V9"/>
+    <hyperlink ref="J16" r:id="rId73" tooltip="https://www.amazon.fr/dp/B0F9NJM4V9?psc=1"/>
+    <hyperlink ref="K16" r:id="rId74" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61GdOBS8v+L._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L16" r:id="rId75" tooltip="https://www.amazon.fr/dp/B0F9NJM4V9"/>
+    <hyperlink ref="C17" r:id="rId76" tooltip="https://www.amazon.fr/dp/B0FDWVV95V"/>
     <hyperlink ref="G17" r:id="rId77" tooltip="https://www.amazon.frundefined"/>
-    <hyperlink ref="J17" r:id="rId78" tooltip="https://www.amazon.fr/dp/B0F9NJM4V9?psc=1"/>
-    <hyperlink ref="K17" r:id="rId79" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61GdOBS8v+L._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L17" r:id="rId80" tooltip="https://www.amazon.fr/dp/B0F9NJM4V9"/>
-    <hyperlink ref="C18" r:id="rId81" tooltip="https://www.amazon.fr/dp/B0FDWVV95V"/>
+    <hyperlink ref="J17" r:id="rId78" tooltip="https://www.amazon.fr/dp/B0FDWVV95V?psc=1"/>
+    <hyperlink ref="K17" r:id="rId79" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61tL+-AcL6L._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L17" r:id="rId80" tooltip="https://www.amazon.fr/dp/B0FDWVV95V"/>
+    <hyperlink ref="C18" r:id="rId81" tooltip="https://www.amazon.fr/dp/B0FN3V6RFQ"/>
     <hyperlink ref="G18" r:id="rId82" tooltip="https://www.amazon.frundefined"/>
-    <hyperlink ref="J18" r:id="rId83" tooltip="https://www.amazon.fr/dp/B0FDWVV95V?psc=1"/>
-    <hyperlink ref="K18" r:id="rId84" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61tL+-AcL6L._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L18" r:id="rId85" tooltip="https://www.amazon.fr/dp/B0FDWVV95V"/>
-    <hyperlink ref="C19" r:id="rId86" tooltip="https://www.amazon.fr/dp/B0FN3V6RFQ"/>
+    <hyperlink ref="J18" r:id="rId83" tooltip="https://www.amazon.fr/dp/B0FN3V6RFQ?psc=1"/>
+    <hyperlink ref="K18" r:id="rId84" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71YynWtKuIL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L18" r:id="rId85" tooltip="https://www.amazon.fr/dp/B0FN3V6RFQ"/>
+    <hyperlink ref="C19" r:id="rId86" tooltip="https://www.amazon.fr/dp/B0FVS559GZ"/>
     <hyperlink ref="G19" r:id="rId87" tooltip="https://www.amazon.frundefined"/>
-    <hyperlink ref="J19" r:id="rId88" tooltip="https://www.amazon.fr/dp/B0FN3V6RFQ?psc=1"/>
-    <hyperlink ref="K19" r:id="rId89" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71YynWtKuIL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L19" r:id="rId90" tooltip="https://www.amazon.fr/dp/B0FN3V6RFQ"/>
-    <hyperlink ref="C20" r:id="rId91" tooltip="https://www.amazon.fr/dp/B0FVS559GZ"/>
+    <hyperlink ref="J19" r:id="rId88" tooltip="https://www.amazon.fr/dp/B0FVS559GZ?psc=1"/>
+    <hyperlink ref="K19" r:id="rId89" tooltip="https://images-eu.ssl-images-amazon.com/images/I/51dJLeDXofL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L19" r:id="rId90" tooltip="https://www.amazon.fr/dp/B0FVS559GZ"/>
+    <hyperlink ref="C20" r:id="rId91" tooltip="https://www.amazon.fr/dp/B0FY1MB1LJ"/>
     <hyperlink ref="G20" r:id="rId92" tooltip="https://www.amazon.frundefined"/>
-    <hyperlink ref="J20" r:id="rId93" tooltip="https://www.amazon.fr/dp/B0FVS559GZ?psc=1"/>
-    <hyperlink ref="K20" r:id="rId94" tooltip="https://images-eu.ssl-images-amazon.com/images/I/51dJLeDXofL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L20" r:id="rId95" tooltip="https://www.amazon.fr/dp/B0FVS559GZ"/>
-    <hyperlink ref="C21" r:id="rId96" tooltip="https://www.amazon.fr/dp/B0FY1MB1LJ"/>
+    <hyperlink ref="J20" r:id="rId93" tooltip="https://www.amazon.fr/dp/B0FY1MB1LJ?psc=1"/>
+    <hyperlink ref="K20" r:id="rId94" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71JpIWC22rL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L20" r:id="rId95" tooltip="https://www.amazon.fr/dp/B0FY1MB1LJ"/>
+    <hyperlink ref="C21" r:id="rId96" tooltip="https://www.amazon.fr/dp/B0FYM1D13D"/>
     <hyperlink ref="G21" r:id="rId97" tooltip="https://www.amazon.frundefined"/>
-    <hyperlink ref="J21" r:id="rId98" tooltip="https://www.amazon.fr/dp/B0FY1MB1LJ?psc=1"/>
-    <hyperlink ref="K21" r:id="rId99" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71JpIWC22rL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L21" r:id="rId100" tooltip="https://www.amazon.fr/dp/B0FY1MB1LJ"/>
-    <hyperlink ref="C22" r:id="rId101" tooltip="https://www.amazon.fr/dp/B0FYM1D13D"/>
+    <hyperlink ref="J21" r:id="rId98" tooltip="https://www.amazon.fr/dp/B0FYM1D13D?psc=1"/>
+    <hyperlink ref="K21" r:id="rId99" tooltip="https://images-eu.ssl-images-amazon.com/images/I/51dJLeDXofL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L21" r:id="rId100" tooltip="https://www.amazon.fr/dp/B0FYM1D13D"/>
+    <hyperlink ref="C22" r:id="rId101" tooltip="https://www.amazon.fr/dp/B0G4RSJQVT"/>
     <hyperlink ref="G22" r:id="rId102" tooltip="https://www.amazon.frundefined"/>
-    <hyperlink ref="J22" r:id="rId103" tooltip="https://www.amazon.fr/dp/B0FYM1D13D?psc=1"/>
-    <hyperlink ref="K22" r:id="rId104" tooltip="https://images-eu.ssl-images-amazon.com/images/I/51dJLeDXofL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L22" r:id="rId105" tooltip="https://www.amazon.fr/dp/B0FYM1D13D"/>
-    <hyperlink ref="C23" r:id="rId106" tooltip="https://www.amazon.fr/dp/B0G4RSJQVT"/>
+    <hyperlink ref="J22" r:id="rId103" tooltip="https://www.amazon.fr/dp/B0G4RSJQVT?psc=1"/>
+    <hyperlink ref="K22" r:id="rId104" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71mJa10XC6L._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L22" r:id="rId105" tooltip="https://www.amazon.fr/dp/B0G4RSJQVT"/>
+    <hyperlink ref="C23" r:id="rId106" tooltip="https://www.amazon.fr/dp/B0GF7CNTYL"/>
     <hyperlink ref="G23" r:id="rId107" tooltip="https://www.amazon.frundefined"/>
-    <hyperlink ref="J23" r:id="rId108" tooltip="https://www.amazon.fr/dp/B0G4RSJQVT?psc=1"/>
-    <hyperlink ref="K23" r:id="rId109" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71mJa10XC6L._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L23" r:id="rId110" tooltip="https://www.amazon.fr/dp/B0G4RSJQVT"/>
-    <hyperlink ref="C24" r:id="rId111" tooltip="https://www.amazon.fr/dp/B0GF7CNTYL"/>
+    <hyperlink ref="J23" r:id="rId108" tooltip="https://www.amazon.fr/dp/B0GF7CNTYL?psc=1"/>
+    <hyperlink ref="K23" r:id="rId109" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71H9bRmoUnL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L23" r:id="rId110" tooltip="https://www.amazon.fr/dp/B0GF7CNTYL"/>
+    <hyperlink ref="C24" r:id="rId111" tooltip="https://www.amazon.fr/dp/B0GGBLWNRZ"/>
     <hyperlink ref="G24" r:id="rId112" tooltip="https://www.amazon.frundefined"/>
-    <hyperlink ref="J24" r:id="rId113" tooltip="https://www.amazon.fr/dp/B0GF7CNTYL?psc=1"/>
-    <hyperlink ref="K24" r:id="rId114" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71H9bRmoUnL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L24" r:id="rId115" tooltip="https://www.amazon.fr/dp/B0GF7CNTYL"/>
-    <hyperlink ref="C25" r:id="rId116" tooltip="https://www.amazon.fr/dp/B0GGBLWNRZ"/>
+    <hyperlink ref="J24" r:id="rId113" tooltip="https://www.amazon.fr/dp/B0GGBLWNRZ?psc=1"/>
+    <hyperlink ref="K24" r:id="rId114" tooltip="https://images-eu.ssl-images-amazon.com/images/I/41xNIs1B-1L._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L24" r:id="rId115" tooltip="https://www.amazon.fr/dp/B0GGBLWNRZ"/>
+    <hyperlink ref="C25" r:id="rId116" tooltip="https://www.amazon.fr/dp/B0GMPVWCZM"/>
     <hyperlink ref="G25" r:id="rId117" tooltip="https://www.amazon.frundefined"/>
-    <hyperlink ref="J25" r:id="rId118" tooltip="https://www.amazon.fr/dp/B0GGBLWNRZ?psc=1"/>
-    <hyperlink ref="K25" r:id="rId119" tooltip="https://images-eu.ssl-images-amazon.com/images/I/41xNIs1B-1L._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L25" r:id="rId120" tooltip="https://www.amazon.fr/dp/B0GGBLWNRZ"/>
-    <hyperlink ref="C26" r:id="rId121" tooltip="https://www.amazon.fr/dp/B0GMPVWCZM"/>
+    <hyperlink ref="J25" r:id="rId118" tooltip="https://www.amazon.fr/dp/B0GMPVWCZM?psc=1"/>
+    <hyperlink ref="K25" r:id="rId119" tooltip="https://images-eu.ssl-images-amazon.com/images/I/81J2yw2XZnL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L25" r:id="rId120" tooltip="https://www.amazon.fr/dp/B0GMPVWCZM"/>
+    <hyperlink ref="C26" r:id="rId121" tooltip="https://www.amazon.fr/dp/B0GQSRHH7M"/>
     <hyperlink ref="G26" r:id="rId122" tooltip="https://www.amazon.frundefined"/>
-    <hyperlink ref="J26" r:id="rId123" tooltip="https://www.amazon.fr/dp/B0GMPVWCZM?psc=1"/>
-    <hyperlink ref="K26" r:id="rId124" tooltip="https://images-eu.ssl-images-amazon.com/images/I/81J2yw2XZnL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L26" r:id="rId125" tooltip="https://www.amazon.fr/dp/B0GMPVWCZM"/>
-    <hyperlink ref="C27" r:id="rId126" tooltip="https://www.amazon.fr/dp/B0GQSRHH7M"/>
+    <hyperlink ref="J26" r:id="rId123" tooltip="https://www.amazon.fr/dp/B0GQSRHH7M?psc=1"/>
+    <hyperlink ref="K26" r:id="rId124" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61BzcWHyvIL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L26" r:id="rId125" tooltip="https://www.amazon.fr/dp/B0GQSRHH7M"/>
+    <hyperlink ref="C27" r:id="rId126" tooltip="https://www.amazon.fr/dp/B0GT17NK5X"/>
     <hyperlink ref="G27" r:id="rId127" tooltip="https://www.amazon.frundefined"/>
-    <hyperlink ref="J27" r:id="rId128" tooltip="https://www.amazon.fr/dp/B0GQSRHH7M?psc=1"/>
-    <hyperlink ref="K27" r:id="rId129" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61BzcWHyvIL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L27" r:id="rId130" tooltip="https://www.amazon.fr/dp/B0GQSRHH7M"/>
-    <hyperlink ref="C28" r:id="rId131" tooltip="https://www.amazon.fr/dp/B0GT17NK5X"/>
+    <hyperlink ref="J27" r:id="rId128" tooltip="https://www.amazon.fr/dp/B0GT17NK5X?psc=1"/>
+    <hyperlink ref="K27" r:id="rId129" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71ZkgBFQnaL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L27" r:id="rId130" tooltip="https://www.amazon.fr/dp/B0GT17NK5X"/>
+    <hyperlink ref="C28" r:id="rId131" tooltip="https://www.amazon.fr/dp/B0GTYZLWW3"/>
     <hyperlink ref="G28" r:id="rId132" tooltip="https://www.amazon.frundefined"/>
-    <hyperlink ref="J28" r:id="rId133" tooltip="https://www.amazon.fr/dp/B0GT17NK5X?psc=1"/>
-    <hyperlink ref="K28" r:id="rId134" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71ZkgBFQnaL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L28" r:id="rId135" tooltip="https://www.amazon.fr/dp/B0GT17NK5X"/>
-    <hyperlink ref="C29" r:id="rId136" tooltip="https://www.amazon.fr/dp/B0GTYZLWW3"/>
+    <hyperlink ref="J28" r:id="rId133" tooltip="https://www.amazon.fr/dp/B0GTYZLWW3?psc=1"/>
+    <hyperlink ref="K28" r:id="rId134" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71RQJ5XzBgL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L28" r:id="rId135" tooltip="https://www.amazon.fr/dp/B0GTYZLWW3"/>
+    <hyperlink ref="C29" r:id="rId136" tooltip="https://www.amazon.fr/dp/B0GWD94VPC"/>
     <hyperlink ref="G29" r:id="rId137" tooltip="https://www.amazon.frundefined"/>
-    <hyperlink ref="J29" r:id="rId138" tooltip="https://www.amazon.fr/dp/B0GTYZLWW3?psc=1"/>
-    <hyperlink ref="K29" r:id="rId139" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71RQJ5XzBgL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L29" r:id="rId140" tooltip="https://www.amazon.fr/dp/B0GTYZLWW3"/>
-    <hyperlink ref="C30" r:id="rId141" tooltip="https://www.amazon.fr/dp/B0GWD94VPC"/>
+    <hyperlink ref="J29" r:id="rId138" tooltip="https://www.amazon.fr/dp/B0GWD94VPC?psc=1"/>
+    <hyperlink ref="K29" r:id="rId139" tooltip="https://images-eu.ssl-images-amazon.com/images/I/713CpLpTocL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L29" r:id="rId140" tooltip="https://www.amazon.fr/dp/B0GWD94VPC"/>
+    <hyperlink ref="C30" r:id="rId141" tooltip="https://www.amazon.fr/dp/B0GWH1FGJB"/>
     <hyperlink ref="G30" r:id="rId142" tooltip="https://www.amazon.frundefined"/>
-    <hyperlink ref="J30" r:id="rId143" tooltip="https://www.amazon.fr/dp/B0GWD94VPC?psc=1"/>
-    <hyperlink ref="K30" r:id="rId144" tooltip="https://images-eu.ssl-images-amazon.com/images/I/713CpLpTocL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L30" r:id="rId145" tooltip="https://www.amazon.fr/dp/B0GWD94VPC"/>
-    <hyperlink ref="C31" r:id="rId146" tooltip="https://www.amazon.fr/dp/B0GWH1FGJB"/>
+    <hyperlink ref="J30" r:id="rId143" tooltip="https://www.amazon.fr/dp/B0GWH1FGJB?psc=1"/>
+    <hyperlink ref="K30" r:id="rId144" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61J8ToT-vJL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L30" r:id="rId145" tooltip="https://www.amazon.fr/dp/B0GWH1FGJB"/>
+    <hyperlink ref="C31" r:id="rId146" tooltip="https://www.amazon.fr/dp/B0GX27JHM5"/>
     <hyperlink ref="G31" r:id="rId147" tooltip="https://www.amazon.frundefined"/>
-    <hyperlink ref="J31" r:id="rId148" tooltip="https://www.amazon.fr/dp/B0GWH1FGJB?psc=1"/>
-    <hyperlink ref="K31" r:id="rId149" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61J8ToT-vJL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L31" r:id="rId150" tooltip="https://www.amazon.fr/dp/B0GWH1FGJB"/>
-    <hyperlink ref="C32" r:id="rId151" tooltip="https://www.amazon.fr/dp/B0GX27JHM5"/>
+    <hyperlink ref="J31" r:id="rId148" tooltip="https://www.amazon.fr/dp/B0GX27JHM5?psc=1"/>
+    <hyperlink ref="K31" r:id="rId149" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61ZZVDtLmcL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L31" r:id="rId150" tooltip="https://www.amazon.fr/dp/B0GX27JHM5"/>
+    <hyperlink ref="C32" r:id="rId151" tooltip="https://www.amazon.fr/dp/B0GYS43G8G"/>
     <hyperlink ref="G32" r:id="rId152" tooltip="https://www.amazon.frundefined"/>
-    <hyperlink ref="J32" r:id="rId153" tooltip="https://www.amazon.fr/dp/B0GX27JHM5?psc=1"/>
-    <hyperlink ref="K32" r:id="rId154" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61ZZVDtLmcL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L32" r:id="rId155" tooltip="https://www.amazon.fr/dp/B0GX27JHM5"/>
-    <hyperlink ref="C33" r:id="rId156" tooltip="https://www.amazon.fr/dp/B0GYS43G8G"/>
+    <hyperlink ref="J32" r:id="rId153" tooltip="https://www.amazon.fr/dp/B0GYS43G8G?psc=1"/>
+    <hyperlink ref="K32" r:id="rId154" tooltip="https://images-eu.ssl-images-amazon.com/images/I/51JXrvAAoZL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L32" r:id="rId155" tooltip="https://www.amazon.fr/dp/B0GYS43G8G"/>
+    <hyperlink ref="C33" r:id="rId156" tooltip="https://www.amazon.fr/dp/B0H1HSF3G6"/>
     <hyperlink ref="G33" r:id="rId157" tooltip="https://www.amazon.frundefined"/>
-    <hyperlink ref="J33" r:id="rId158" tooltip="https://www.amazon.fr/dp/B0GYS43G8G?psc=1"/>
-    <hyperlink ref="K33" r:id="rId159" tooltip="https://images-eu.ssl-images-amazon.com/images/I/51JXrvAAoZL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L33" r:id="rId160" tooltip="https://www.amazon.fr/dp/B0GYS43G8G"/>
-    <hyperlink ref="C34" r:id="rId161" tooltip="https://www.amazon.fr/dp/B0H1HSF3G6"/>
+    <hyperlink ref="J33" r:id="rId158" tooltip="https://www.amazon.fr/dp/B0H1HSF3G6?psc=1"/>
+    <hyperlink ref="K33" r:id="rId159" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71bkUyyVyuL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L33" r:id="rId160" tooltip="https://www.amazon.fr/dp/B0H1HSF3G6"/>
+    <hyperlink ref="C34" r:id="rId161" tooltip="https://www.amazon.fr/dp/B0H418FY5Y"/>
     <hyperlink ref="G34" r:id="rId162" tooltip="https://www.amazon.frundefined"/>
-    <hyperlink ref="J34" r:id="rId163" tooltip="https://www.amazon.fr/dp/B0H1HSF3G6?psc=1"/>
-    <hyperlink ref="K34" r:id="rId164" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71bkUyyVyuL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L34" r:id="rId165" tooltip="https://www.amazon.fr/dp/B0H1HSF3G6"/>
-    <hyperlink ref="C35" r:id="rId166" tooltip="https://www.amazon.fr/dp/B0H418FY5Y"/>
+    <hyperlink ref="J34" r:id="rId163" tooltip="https://www.amazon.fr/dp/B0H418FY5Y?psc=1"/>
+    <hyperlink ref="K34" r:id="rId164" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61InrYvl2-L._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L34" r:id="rId165" tooltip="https://www.amazon.fr/dp/B0H418FY5Y"/>
+    <hyperlink ref="C35" r:id="rId166" tooltip="https://www.amazon.fr/dp/B0H6F2NPXK"/>
     <hyperlink ref="G35" r:id="rId167" tooltip="https://www.amazon.frundefined"/>
-    <hyperlink ref="J35" r:id="rId168" tooltip="https://www.amazon.fr/dp/B0H418FY5Y?psc=1"/>
+    <hyperlink ref="J35" r:id="rId168" tooltip="https://www.amazon.fr/dp/B0H6F2NPXK?psc=1"/>
     <hyperlink ref="K35" r:id="rId169" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61InrYvl2-L._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L35" r:id="rId170" tooltip="https://www.amazon.fr/dp/B0H418FY5Y"/>
-    <hyperlink ref="C36" r:id="rId171" tooltip="https://www.amazon.fr/dp/B0H6F2NPXK"/>
+    <hyperlink ref="L35" r:id="rId170" tooltip="https://www.amazon.fr/dp/B0H6F2NPXK"/>
+    <hyperlink ref="C36" r:id="rId171" tooltip="https://www.amazon.fr/dp/B0H7WRJXL5"/>
     <hyperlink ref="G36" r:id="rId172" tooltip="https://www.amazon.frundefined"/>
-    <hyperlink ref="J36" r:id="rId173" tooltip="https://www.amazon.fr/dp/B0H6F2NPXK?psc=1"/>
-    <hyperlink ref="K36" r:id="rId174" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61InrYvl2-L._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L36" r:id="rId175" tooltip="https://www.amazon.fr/dp/B0H6F2NPXK"/>
-    <hyperlink ref="C37" r:id="rId176" tooltip="https://www.amazon.fr/dp/B0H7WRJXL5"/>
+    <hyperlink ref="J36" r:id="rId173" tooltip="https://www.amazon.fr/dp/B0H7WRJXL5?psc=1"/>
+    <hyperlink ref="K36" r:id="rId174" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71pvlE5JbtL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L36" r:id="rId175" tooltip="https://www.amazon.fr/dp/B0H7WRJXL5"/>
+    <hyperlink ref="C37" r:id="rId176" tooltip="https://www.amazon.fr/dp/B0H8Z6R4ZK"/>
     <hyperlink ref="G37" r:id="rId177" tooltip="https://www.amazon.frundefined"/>
-    <hyperlink ref="J37" r:id="rId178" tooltip="https://www.amazon.fr/dp/B0H7WRJXL5?psc=1"/>
-    <hyperlink ref="K37" r:id="rId179" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71pvlE5JbtL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L37" r:id="rId180" tooltip="https://www.amazon.fr/dp/B0H7WRJXL5"/>
-    <hyperlink ref="C38" r:id="rId181" tooltip="https://www.amazon.fr/dp/B0H8Z6R4ZK"/>
+    <hyperlink ref="J37" r:id="rId178" tooltip="https://www.amazon.fr/dp/B0H8Z6R4ZK?psc=1"/>
+    <hyperlink ref="K37" r:id="rId179" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61HKr6BnAHL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L37" r:id="rId180" tooltip="https://www.amazon.fr/dp/B0H8Z6R4ZK"/>
+    <hyperlink ref="C38" r:id="rId181" tooltip="https://www.amazon.fr/dp/B0HG11J16S"/>
     <hyperlink ref="G38" r:id="rId182" tooltip="https://www.amazon.frundefined"/>
-    <hyperlink ref="J38" r:id="rId183" tooltip="https://www.amazon.fr/dp/B0H8Z6R4ZK?psc=1"/>
-    <hyperlink ref="K38" r:id="rId184" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61HKr6BnAHL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L38" r:id="rId185" tooltip="https://www.amazon.fr/dp/B0H8Z6R4ZK"/>
-    <hyperlink ref="C39" r:id="rId186" tooltip="https://www.amazon.fr/dp/B0HG11J16S"/>
-    <hyperlink ref="G39" r:id="rId187" tooltip="https://www.amazon.frundefined"/>
-    <hyperlink ref="J39" r:id="rId188" tooltip="https://www.amazon.fr/dp/B0HG11J16S?psc=1"/>
-    <hyperlink ref="K39" r:id="rId189" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71pvlE5JbtL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L39" r:id="rId190" tooltip="https://www.amazon.fr/dp/B0HG11J16S"/>
+    <hyperlink ref="J38" r:id="rId183" tooltip="https://www.amazon.fr/dp/B0HG11J16S?psc=1"/>
+    <hyperlink ref="K38" r:id="rId184" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71pvlE5JbtL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L38" r:id="rId185" tooltip="https://www.amazon.fr/dp/B0HG11J16S"/>
   </hyperlinks>
-  <drawing r:id="rId191"/>
+  <drawing r:id="rId186"/>
 </worksheet>
 </file>
 
